--- a/sheets/민요/검수/사발가.xlsx
+++ b/sheets/민요/검수/사발가.xlsx
@@ -4,14 +4,14 @@
   <sheets>
     <sheet name="정보" sheetId="1" r:id="rId1"/>
     <sheet name="정간목록" sheetId="2" r:id="rId2"/>
-    <sheet name="악보 1" sheetId="3" r:id="rId3"/>
+    <sheet name="악보" sheetId="3" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <name val="맑은 고딕"/>
@@ -20,6 +20,26 @@
     <font>
       <b/>
       <sz val="11"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <sz val="22"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="13"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
     </font>
@@ -50,7 +70,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -73,11 +93,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -96,6 +131,18 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2625,8 +2672,12 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
+  <dimension ref="A1:I18"/>
   <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="9" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
     <col min="4" max="4" width="9" customWidth="1"/>
@@ -2637,730 +2688,730 @@
     <col min="9" max="9" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">사발가 — 민요채보-2/사발가.png</t>
-        </is>
-      </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">정간</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4줄</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3줄</t>
-        </is>
-      </c>
-      <c r="E2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="F2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2줄</t>
-        </is>
-      </c>
-      <c r="G2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="H2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1줄</t>
-        </is>
-      </c>
-      <c r="I2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="32" customHeight="1">
-      <c r="A3" s="1">
-        <v>1</v>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
+    <row r="1"/>
+    <row r="2" ht="60" customHeight="1">
+      <c s="8" t="inlineStr" r="B2">
+        <is>
+          <t xml:space="preserve">사발가</t>
+        </is>
+      </c>
+      <c s="8" r="C2"/>
+      <c s="8" r="D2"/>
+      <c s="8" r="E2"/>
+      <c s="8" r="F2"/>
+      <c s="8" r="G2"/>
+      <c s="8" r="H2"/>
+      <c s="8" r="I2"/>
+    </row>
+    <row r="3" ht="56" customHeight="1">
+      <c r="B3" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 汰</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">허</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I3" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">석</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="1">
-        <v>2</v>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+    <row r="4" ht="56" customHeight="1">
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 無</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="C4" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">송</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="E4" s="10"/>
+      <c r="F4" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 潢</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">니</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H4" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="I4" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">탄</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="1">
-        <v>3</v>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
+    <row r="5" ht="56" customHeight="1">
+      <c r="B5" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">세</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 林</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E5" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">혜</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="H5" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I5" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">백</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="32" customHeight="1">
-      <c r="A6" s="1">
-        <v>4</v>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
+    <row r="6" ht="56" customHeight="1">
+      <c r="B6" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 林</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">월</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 林</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E6" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">요</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="G6" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">슴</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="H6" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="I6" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">탄</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="48" customHeight="1">
-      <c r="A7" s="1">
-        <v>5</v>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
+    <row r="7" ht="56" customHeight="1">
+      <c r="B7" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">林</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">을</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E7" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F7" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">淋</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G7" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">타</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="H7" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 仲
 汰</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="I7" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">타</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="32" customHeight="1">
-      <c r="A8" s="1">
-        <v>6</v>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
+    <row r="8" ht="56" customHeight="1">
+      <c r="B8" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 林</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C8" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">잡</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 無</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="E8" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">혜</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F8" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 淋</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G8" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">는</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="H8" s="9" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="I8" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">는</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="48" customHeight="1">
-      <c r="A9" s="1">
-        <v>7</v>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
+    <row r="9" ht="56" customHeight="1">
+      <c r="B9" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C9" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D9" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E9" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F9" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G9" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">데</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢
-―
+      <c r="H9" s="9" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">潢
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 汰</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="I9" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">데</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="32" customHeight="1">
-      <c r="A10" s="1">
-        <v>8</v>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
+    <row r="10" ht="56" customHeight="1">
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">라</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="E10" s="10"/>
+      <c r="F10" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰</t>
         </is>
       </c>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="G10" s="10"/>
+      <c r="H10" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰</t>
         </is>
       </c>
-      <c r="I10" s="2"/>
-    </row>
-    <row r="11" ht="32" customHeight="1">
-      <c r="A11" s="1">
-        <v>9</v>
-      </c>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="I10" s="10"/>
+    </row>
+    <row r="11" ht="56" customHeight="1">
+      <c r="B11" s="9"/>
+      <c r="C11" s="10"/>
+      <c r="D11" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E11" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F11" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 汰</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G11" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">연</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H11" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 汰</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="I11" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">연</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="32" customHeight="1">
-      <c r="A12" s="1">
-        <v>10</v>
-      </c>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2" t="inlineStr">
+    <row r="12" ht="56" customHeight="1">
+      <c r="B12" s="9"/>
+      <c r="C12" s="10"/>
+      <c r="D12" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E12" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">머</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 汰</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="G12" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">기</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H12" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 汰</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="I12" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">기</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="48" customHeight="1">
-      <c r="A13" s="1">
-        <v>11</v>
-      </c>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2" t="inlineStr">
+    <row r="13" ht="56" customHeight="1">
+      <c r="B13" s="9"/>
+      <c r="C13" s="10"/>
+      <c r="D13" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E13" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F13" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 姑
 林</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G13" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">도</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="H13" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 林</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="I13" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="32" customHeight="1">
-      <c r="A14" s="1">
-        <v>12</v>
-      </c>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2" t="inlineStr">
+    <row r="14" ht="56" customHeight="1">
+      <c r="B14" s="9"/>
+      <c r="C14" s="10"/>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="E14" s="10"/>
+      <c r="F14" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 林</t>
         </is>
       </c>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="G14" s="10"/>
+      <c r="H14" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 林</t>
         </is>
       </c>
-      <c r="I14" s="2"/>
-    </row>
-    <row r="15" ht="48" customHeight="1">
-      <c r="A15" s="1">
-        <v>13</v>
-      </c>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="I14" s="10"/>
+    </row>
+    <row r="15" ht="56" customHeight="1">
+      <c r="B15" s="9"/>
+      <c r="C15" s="10"/>
+      <c r="D15" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">淋
 潢</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E15" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F15" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 姑
 無</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="G15" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">김</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="H15" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 無</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
+      <c r="I15" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">펄</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="32" customHeight="1">
-      <c r="A16" s="1">
-        <v>14</v>
-      </c>
-      <c r="B16" s="2"/>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2" t="inlineStr">
+    <row r="16" ht="56" customHeight="1">
+      <c r="B16" s="9"/>
+      <c r="C16" s="10"/>
+      <c r="D16" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">淋
 汰</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E16" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">여</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F16" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 無</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G16" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">도</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="H16" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 姑</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="I16" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">펄</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="1">
-        <v>15</v>
-      </c>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2" t="inlineStr">
+    <row r="17" ht="56" customHeight="1">
+      <c r="B17" s="9"/>
+      <c r="C17" s="10"/>
+      <c r="D17" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E17" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">라</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F17" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G17" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">안</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="H17" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="I17" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="32" customHeight="1">
-      <c r="A18" s="1">
-        <v>16</v>
-      </c>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2" t="inlineStr">
+    <row r="18" ht="56" customHeight="1">
+      <c r="B18" s="9"/>
+      <c r="C18" s="10"/>
+      <c r="D18" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">淋
 汰</t>
         </is>
       </c>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="E18" s="10"/>
+      <c r="F18" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G18" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="H18" s="9" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
+      <c r="I18" s="10" t="inlineStr">
         <is>
           <t xml:space="preserve">지</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:I2"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" fitToWidth="1" fitToHeight="0" scale="77"/>
 </worksheet>
 </file>
--- a/sheets/민요/검수/사발가.xlsx
+++ b/sheets/민요/검수/사발가.xlsx
@@ -405,7 +405,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">― 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
+          <t xml:space="preserve">– 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
         </is>
       </c>
     </row>
@@ -585,12 +585,12 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|汰</t>
+          <t xml:space="preserve">–|汰</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 汰</t>
         </is>
       </c>
@@ -657,12 +657,12 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I5" s="2"/>
@@ -1059,13 +1059,13 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑|―</t>
+          <t xml:space="preserve">姑|–</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-―</t>
+–</t>
         </is>
       </c>
       <c r="I16" s="2"/>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|汰</t>
+          <t xml:space="preserve">–|汰</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 汰</t>
         </is>
       </c>
@@ -1242,12 +1242,12 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I21" s="2"/>
@@ -1636,13 +1636,13 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑|―</t>
+          <t xml:space="preserve">姑|–</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-―</t>
+–</t>
         </is>
       </c>
       <c r="I32" s="2"/>
@@ -1707,13 +1707,13 @@
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南|―</t>
+          <t xml:space="preserve">南|–</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-―</t>
+–</t>
         </is>
       </c>
       <c r="I34" s="2"/>
@@ -1850,13 +1850,13 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南|―</t>
+          <t xml:space="preserve">南|–</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-―</t>
+–</t>
         </is>
       </c>
       <c r="I38" s="2"/>
@@ -1921,13 +1921,13 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南|―</t>
+          <t xml:space="preserve">南|–</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-―</t>
+–</t>
         </is>
       </c>
       <c r="I40" s="2"/>
@@ -2247,13 +2247,13 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑|―</t>
+          <t xml:space="preserve">姑|–</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-―</t>
+–</t>
         </is>
       </c>
       <c r="I49" s="2"/>
@@ -2283,14 +2283,14 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">無|汰|―|無</t>
+          <t xml:space="preserve">無|汰|–|無</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 汰
-―
+–
 無</t>
         </is>
       </c>
@@ -2396,13 +2396,13 @@
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑|―|△</t>
+          <t xml:space="preserve">姑|–|△</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-―
+–
 △</t>
         </is>
       </c>
@@ -2433,14 +2433,14 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|汰|―</t>
+          <t xml:space="preserve">潢|汰|–</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰
-―</t>
+–</t>
         </is>
       </c>
       <c r="I54" s="2"/>
@@ -2506,13 +2506,13 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南|―</t>
+          <t xml:space="preserve">南|–</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-―</t>
+–</t>
         </is>
       </c>
       <c r="I56" s="2"/>
@@ -2542,13 +2542,13 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南|―|△</t>
+          <t xml:space="preserve">南|–|△</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-―
+–
 △</t>
         </is>
       </c>
@@ -2579,14 +2579,14 @@
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|汰|―|潢</t>
+          <t xml:space="preserve">潢|汰|–|潢</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰
-―
+–
 潢</t>
         </is>
       </c>
@@ -2617,14 +2617,14 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|仲|―</t>
+          <t xml:space="preserve">潢|仲|–</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 仲
-―</t>
+–</t>
         </is>
       </c>
       <c r="I59" s="2"/>
@@ -2691,13 +2691,13 @@
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南|―|△</t>
+          <t xml:space="preserve">南|–|△</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-―
+–
 △</t>
         </is>
       </c>
@@ -2802,13 +2802,13 @@
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|―</t>
+          <t xml:space="preserve">潢|–</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―</t>
+–</t>
         </is>
       </c>
       <c r="I64" s="2"/>
@@ -2895,7 +2895,7 @@
         <is>
           <t xml:space="preserve">無
 汰
-―
+–
 無</t>
         </is>
       </c>
@@ -2903,7 +2903,7 @@
       <c r="D3" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-―</t>
+–</t>
         </is>
       </c>
       <c r="E3" s="2"/>
@@ -2941,14 +2941,14 @@
       <c r="E4" s="2"/>
       <c r="F4" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 汰</t>
         </is>
       </c>
       <c r="G4" s="2"/>
       <c r="H4" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 汰</t>
         </is>
       </c>
@@ -2991,7 +2991,7 @@
       <c r="B6" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-―
+–
 △</t>
         </is>
       </c>
@@ -3005,13 +3005,13 @@
       <c r="E6" s="2"/>
       <c r="F6" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="G6" s="2"/>
       <c r="H6" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I6" s="2"/>
@@ -3022,14 +3022,14 @@
         <is>
           <t xml:space="preserve">潢
 汰
-―</t>
+–</t>
         </is>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-―</t>
+–</t>
         </is>
       </c>
       <c r="E7" s="2"/>
@@ -3083,14 +3083,14 @@
       <c r="B9" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-―</t>
+–</t>
         </is>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-―</t>
+–</t>
         </is>
       </c>
       <c r="E9" s="2"/>
@@ -3114,7 +3114,7 @@
       <c r="B10" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-―
+–
 △</t>
         </is>
       </c>
@@ -3146,7 +3146,7 @@
         <is>
           <t xml:space="preserve">潢
 汰
-―
+–
 潢</t>
         </is>
       </c>
@@ -3180,7 +3180,7 @@
         <is>
           <t xml:space="preserve">潢
 仲
-―</t>
+–</t>
         </is>
       </c>
       <c r="C12" s="2"/>
@@ -3242,7 +3242,7 @@
       <c r="B14" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-―
+–
 △</t>
         </is>
       </c>
@@ -3340,7 +3340,7 @@
       <c r="B17" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―</t>
+–</t>
         </is>
       </c>
       <c r="C17" s="2"/>
@@ -3353,14 +3353,14 @@
       <c r="F17" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-―</t>
+–</t>
         </is>
       </c>
       <c r="G17" s="2"/>
       <c r="H17" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-―</t>
+–</t>
         </is>
       </c>
       <c r="I17" s="2"/>
@@ -3378,7 +3378,7 @@
       <c r="D18" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-―</t>
+–</t>
         </is>
       </c>
       <c r="E18" s="2"/>

--- a/sheets/민요/검수/사발가.xlsx
+++ b/sheets/민요/검수/사발가.xlsx
@@ -11,27 +11,43 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="4">
+  <fonts count="7">
     <font>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="22"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -134,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -157,7 +173,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <!-- 8~16: 박 묶음 가사 칸 = (일반 8~10 · 비고 11~13 · 팔레트 외 14~16) × (첫 · 가운데 · 마지막) -->
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -185,7 +200,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <!-- 17~19: 악보 율명 칸 22pt (가사 11pt 의 두 배) = 일반 · 비고 · 팔레트 외 -->
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -193,6 +207,21 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2876,22 +2905,22 @@
     </row>
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="0"/>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">사발가</t>
         </is>
       </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
     </row>
     <row r="3" ht="56" customHeight="1">
       <c r="A3" s="0"/>
-      <c r="B3" s="17" t="inlineStr">
+      <c r="B3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 汰
@@ -2899,32 +2928,32 @@
 無</t>
         </is>
       </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="17" t="inlineStr">
+      <c r="C3" s="22"/>
+      <c r="D3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 –</t>
         </is>
       </c>
-      <c r="E3" s="2"/>
-      <c r="F3" s="17" t="inlineStr">
+      <c r="E3" s="22"/>
+      <c r="F3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 潢</t>
         </is>
       </c>
-      <c r="G3" s="2"/>
-      <c r="H3" s="18" t="inlineStr">
+      <c r="G3" s="22"/>
+      <c r="H3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 潢</t>
         </is>
       </c>
-      <c r="I3" s="3"/>
+      <c r="I3" s="24"/>
     </row>
     <row r="4" ht="56" customHeight="1">
       <c r="A4" s="0"/>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 林
@@ -2932,217 +2961,217 @@
 林</t>
         </is>
       </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="17" t="inlineStr">
+      <c r="C4" s="22"/>
+      <c r="D4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="E4" s="2"/>
-      <c r="F4" s="17" t="inlineStr">
+      <c r="E4" s="22"/>
+      <c r="F4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 汰</t>
         </is>
       </c>
-      <c r="G4" s="2"/>
-      <c r="H4" s="17" t="inlineStr">
+      <c r="G4" s="22"/>
+      <c r="H4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 汰</t>
         </is>
       </c>
-      <c r="I4" s="2"/>
+      <c r="I4" s="22"/>
     </row>
     <row r="5" ht="56" customHeight="1">
       <c r="A5" s="0"/>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 無
 南</t>
         </is>
       </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="17" t="inlineStr">
+      <c r="C5" s="22"/>
+      <c r="D5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 林</t>
         </is>
       </c>
-      <c r="E5" s="2"/>
-      <c r="F5" s="17" t="inlineStr">
+      <c r="E5" s="22"/>
+      <c r="F5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰</t>
         </is>
       </c>
-      <c r="G5" s="2"/>
-      <c r="H5" s="17" t="inlineStr">
+      <c r="G5" s="22"/>
+      <c r="H5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 潢</t>
         </is>
       </c>
-      <c r="I5" s="2"/>
+      <c r="I5" s="22"/>
     </row>
     <row r="6" ht="56" customHeight="1">
       <c r="A6" s="0"/>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 –
 △</t>
         </is>
       </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="17" t="inlineStr">
+      <c r="C6" s="22"/>
+      <c r="D6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 林</t>
         </is>
       </c>
-      <c r="E6" s="2"/>
-      <c r="F6" s="17" t="inlineStr">
+      <c r="E6" s="22"/>
+      <c r="F6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G6" s="2"/>
-      <c r="H6" s="17" t="inlineStr">
+      <c r="G6" s="22"/>
+      <c r="H6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I6" s="2"/>
+      <c r="I6" s="22"/>
     </row>
     <row r="7" ht="56" customHeight="1">
       <c r="A7" s="0"/>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰
 –</t>
         </is>
       </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="17" t="inlineStr">
+      <c r="C7" s="22"/>
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 –</t>
         </is>
       </c>
-      <c r="E7" s="2"/>
-      <c r="F7" s="17" t="inlineStr">
+      <c r="E7" s="22"/>
+      <c r="F7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">淋
 㴌</t>
         </is>
       </c>
-      <c r="G7" s="2"/>
-      <c r="H7" s="18" t="inlineStr">
+      <c r="G7" s="22"/>
+      <c r="H7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 㴌</t>
         </is>
       </c>
-      <c r="I7" s="3"/>
+      <c r="I7" s="24"/>
     </row>
     <row r="8" ht="56" customHeight="1">
       <c r="A8" s="0"/>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 淋</t>
         </is>
       </c>
-      <c r="C8" s="2"/>
-      <c r="D8" s="17" t="inlineStr">
+      <c r="C8" s="22"/>
+      <c r="D8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="E8" s="2"/>
-      <c r="F8" s="17" t="inlineStr">
+      <c r="E8" s="22"/>
+      <c r="F8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰</t>
         </is>
       </c>
-      <c r="G8" s="2"/>
-      <c r="H8" s="17" t="inlineStr">
+      <c r="G8" s="22"/>
+      <c r="H8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰</t>
         </is>
       </c>
-      <c r="I8" s="2"/>
+      <c r="I8" s="22"/>
     </row>
     <row r="9" ht="56" customHeight="1">
       <c r="A9" s="0"/>
-      <c r="B9" s="17" t="inlineStr">
+      <c r="B9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 –</t>
         </is>
       </c>
-      <c r="C9" s="2"/>
-      <c r="D9" s="17" t="inlineStr">
+      <c r="C9" s="22"/>
+      <c r="D9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 –</t>
         </is>
       </c>
-      <c r="E9" s="2"/>
-      <c r="F9" s="17" t="inlineStr">
+      <c r="E9" s="22"/>
+      <c r="F9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 㳞</t>
         </is>
       </c>
-      <c r="G9" s="2"/>
-      <c r="H9" s="18" t="inlineStr">
+      <c r="G9" s="22"/>
+      <c r="H9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 㳞</t>
         </is>
       </c>
-      <c r="I9" s="3"/>
+      <c r="I9" s="24"/>
     </row>
     <row r="10" ht="56" customHeight="1">
       <c r="A10" s="0"/>
-      <c r="B10" s="17" t="inlineStr">
+      <c r="B10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 –
 △</t>
         </is>
       </c>
-      <c r="C10" s="2"/>
-      <c r="D10" s="17" t="inlineStr">
+      <c r="C10" s="22"/>
+      <c r="D10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="E10" s="2"/>
-      <c r="F10" s="17" t="inlineStr">
+      <c r="E10" s="22"/>
+      <c r="F10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰</t>
         </is>
       </c>
-      <c r="G10" s="2"/>
-      <c r="H10" s="17" t="inlineStr">
+      <c r="G10" s="22"/>
+      <c r="H10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰</t>
         </is>
       </c>
-      <c r="I10" s="2"/>
+      <c r="I10" s="22"/>
     </row>
     <row r="11" ht="56" customHeight="1">
       <c r="A11" s="0"/>
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰
@@ -3150,70 +3179,70 @@
 潢</t>
         </is>
       </c>
-      <c r="C11" s="2"/>
-      <c r="D11" s="17" t="inlineStr">
+      <c r="C11" s="22"/>
+      <c r="D11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 汰
 無</t>
         </is>
       </c>
-      <c r="E11" s="2"/>
-      <c r="F11" s="17" t="inlineStr">
+      <c r="E11" s="22"/>
+      <c r="F11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 汰</t>
         </is>
       </c>
-      <c r="G11" s="2"/>
-      <c r="H11" s="17" t="inlineStr">
+      <c r="G11" s="22"/>
+      <c r="H11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 汰</t>
         </is>
       </c>
-      <c r="I11" s="2"/>
+      <c r="I11" s="22"/>
     </row>
     <row r="12" ht="56" customHeight="1">
       <c r="A12" s="0"/>
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 仲
 –</t>
         </is>
       </c>
-      <c r="C12" s="2"/>
-      <c r="D12" s="17" t="inlineStr">
+      <c r="C12" s="22"/>
+      <c r="D12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="E12" s="2"/>
-      <c r="F12" s="17" t="inlineStr">
+      <c r="E12" s="22"/>
+      <c r="F12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">黃</t>
         </is>
       </c>
-      <c r="G12" s="2"/>
-      <c r="H12" s="17" t="inlineStr">
+      <c r="G12" s="22"/>
+      <c r="H12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">黃</t>
         </is>
       </c>
-      <c r="I12" s="2"/>
+      <c r="I12" s="22"/>
     </row>
     <row r="13" ht="56" customHeight="1">
       <c r="A13" s="0"/>
-      <c r="B13" s="17" t="inlineStr">
+      <c r="B13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">淋
 潢
 汰</t>
         </is>
       </c>
-      <c r="C13" s="2"/>
-      <c r="D13" s="17" t="inlineStr">
+      <c r="C13" s="22"/>
+      <c r="D13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 林
@@ -3221,97 +3250,97 @@
 林</t>
         </is>
       </c>
-      <c r="E13" s="2"/>
-      <c r="F13" s="17" t="inlineStr">
+      <c r="E13" s="22"/>
+      <c r="F13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 林</t>
         </is>
       </c>
-      <c r="G13" s="2"/>
-      <c r="H13" s="17" t="inlineStr">
+      <c r="G13" s="22"/>
+      <c r="H13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 林</t>
         </is>
       </c>
-      <c r="I13" s="2"/>
+      <c r="I13" s="22"/>
     </row>
     <row r="14" ht="56" customHeight="1">
       <c r="A14" s="0"/>
-      <c r="B14" s="17" t="inlineStr">
+      <c r="B14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 –
 △</t>
         </is>
       </c>
-      <c r="C14" s="2"/>
-      <c r="D14" s="17" t="inlineStr">
+      <c r="C14" s="22"/>
+      <c r="D14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 無
 林</t>
         </is>
       </c>
-      <c r="E14" s="2"/>
-      <c r="F14" s="17" t="inlineStr">
+      <c r="E14" s="22"/>
+      <c r="F14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 林</t>
         </is>
       </c>
-      <c r="G14" s="2"/>
-      <c r="H14" s="17" t="inlineStr">
+      <c r="G14" s="22"/>
+      <c r="H14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 林</t>
         </is>
       </c>
-      <c r="I14" s="2"/>
+      <c r="I14" s="22"/>
     </row>
     <row r="15" ht="56" customHeight="1">
       <c r="A15" s="0"/>
-      <c r="B15" s="17" t="inlineStr">
+      <c r="B15" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 淋
 汰</t>
         </is>
       </c>
-      <c r="C15" s="2"/>
-      <c r="D15" s="17" t="inlineStr">
+      <c r="C15" s="22"/>
+      <c r="D15" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="E15" s="2"/>
-      <c r="F15" s="17" t="inlineStr">
+      <c r="E15" s="22"/>
+      <c r="F15" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 黃</t>
         </is>
       </c>
-      <c r="G15" s="2"/>
-      <c r="H15" s="17" t="inlineStr">
+      <c r="G15" s="22"/>
+      <c r="H15" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 黃</t>
         </is>
       </c>
-      <c r="I15" s="2"/>
+      <c r="I15" s="22"/>
     </row>
     <row r="16" ht="56" customHeight="1">
       <c r="A16" s="0"/>
-      <c r="B16" s="17" t="inlineStr">
+      <c r="B16" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 淋
 汰</t>
         </is>
       </c>
-      <c r="C16" s="2"/>
-      <c r="D16" s="17" t="inlineStr">
+      <c r="C16" s="22"/>
+      <c r="D16" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 無
@@ -3319,81 +3348,81 @@
 南</t>
         </is>
       </c>
-      <c r="E16" s="2"/>
-      <c r="F16" s="17" t="inlineStr">
+      <c r="E16" s="22"/>
+      <c r="F16" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 林</t>
         </is>
       </c>
-      <c r="G16" s="2"/>
-      <c r="H16" s="17" t="inlineStr">
+      <c r="G16" s="22"/>
+      <c r="H16" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 林</t>
         </is>
       </c>
-      <c r="I16" s="2"/>
+      <c r="I16" s="22"/>
     </row>
     <row r="17" ht="56" customHeight="1">
       <c r="A17" s="0"/>
-      <c r="B17" s="17" t="inlineStr">
+      <c r="B17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 –</t>
         </is>
       </c>
-      <c r="C17" s="2"/>
-      <c r="D17" s="17" t="inlineStr">
+      <c r="C17" s="22"/>
+      <c r="D17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="E17" s="2"/>
-      <c r="F17" s="17" t="inlineStr">
+      <c r="E17" s="22"/>
+      <c r="F17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 –</t>
         </is>
       </c>
-      <c r="G17" s="2"/>
-      <c r="H17" s="17" t="inlineStr">
+      <c r="G17" s="22"/>
+      <c r="H17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 –</t>
         </is>
       </c>
-      <c r="I17" s="2"/>
+      <c r="I17" s="22"/>
     </row>
     <row r="18" ht="56" customHeight="1">
       <c r="A18" s="0"/>
-      <c r="B18" s="17" t="inlineStr">
+      <c r="B18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 淋
 汰</t>
         </is>
       </c>
-      <c r="C18" s="2"/>
-      <c r="D18" s="17" t="inlineStr">
+      <c r="C18" s="22"/>
+      <c r="D18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 –</t>
         </is>
       </c>
-      <c r="E18" s="2"/>
-      <c r="F18" s="17" t="inlineStr">
+      <c r="E18" s="22"/>
+      <c r="F18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林</t>
         </is>
       </c>
-      <c r="G18" s="2"/>
-      <c r="H18" s="18" t="inlineStr">
+      <c r="G18" s="22"/>
+      <c r="H18" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">林</t>
         </is>
       </c>
-      <c r="I18" s="3"/>
+      <c r="I18" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/sheets/민요/검수/사발가.xlsx
+++ b/sheets/민요/검수/사발가.xlsx
@@ -2890,20 +2890,20 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="108.96" customHeight="1">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -2918,7 +2918,7 @@
       <c r="H2" s="20"/>
       <c r="I2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="108.96" customHeight="1">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -2951,7 +2951,7 @@
       </c>
       <c r="I3" s="24"/>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="108.96" customHeight="1">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -2964,7 +2964,7 @@
       <c r="C4" s="22"/>
       <c r="D4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="E4" s="22"/>
@@ -2983,7 +2983,7 @@
       </c>
       <c r="I4" s="22"/>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="108.96" customHeight="1">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -3015,7 +3015,7 @@
       </c>
       <c r="I5" s="22"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="108.96" customHeight="1">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -3045,7 +3045,7 @@
       </c>
       <c r="I6" s="22"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="108.96" customHeight="1">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -3077,7 +3077,7 @@
       </c>
       <c r="I7" s="24"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="108.96" customHeight="1">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -3107,7 +3107,7 @@
       </c>
       <c r="I8" s="22"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="108.96" customHeight="1">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="I9" s="24"/>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="108.96" customHeight="1">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -3150,7 +3150,7 @@
       <c r="C10" s="22"/>
       <c r="D10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="E10" s="22"/>
@@ -3169,7 +3169,7 @@
       </c>
       <c r="I10" s="22"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="108.96" customHeight="1">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -3203,7 +3203,7 @@
       </c>
       <c r="I11" s="22"/>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="108.96" customHeight="1">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -3215,7 +3215,7 @@
       <c r="C12" s="22"/>
       <c r="D12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="E12" s="22"/>
@@ -3232,7 +3232,7 @@
       </c>
       <c r="I12" s="22"/>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="108.96" customHeight="1">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -3266,7 +3266,7 @@
       </c>
       <c r="I13" s="22"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="108.96" customHeight="1">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
       </c>
       <c r="I14" s="22"/>
     </row>
-    <row r="15" ht="56" customHeight="1">
+    <row r="15" ht="108.96" customHeight="1">
       <c r="A15" s="0"/>
       <c r="B15" s="21" t="inlineStr">
         <is>
@@ -3311,7 +3311,7 @@
       <c r="C15" s="22"/>
       <c r="D15" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="E15" s="22"/>
@@ -3330,7 +3330,7 @@
       </c>
       <c r="I15" s="22"/>
     </row>
-    <row r="16" ht="56" customHeight="1">
+    <row r="16" ht="108.96" customHeight="1">
       <c r="A16" s="0"/>
       <c r="B16" s="21" t="inlineStr">
         <is>
@@ -3364,7 +3364,7 @@
       </c>
       <c r="I16" s="22"/>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="108.96" customHeight="1">
       <c r="A17" s="0"/>
       <c r="B17" s="21" t="inlineStr">
         <is>
@@ -3375,7 +3375,7 @@
       <c r="C17" s="22"/>
       <c r="D17" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="E17" s="22"/>
@@ -3394,7 +3394,7 @@
       </c>
       <c r="I17" s="22"/>
     </row>
-    <row r="18" ht="56" customHeight="1">
+    <row r="18" ht="108.96" customHeight="1">
       <c r="A18" s="0"/>
       <c r="B18" s="21" t="inlineStr">
         <is>

--- a/sheets/민요/검수/사발가.xlsx
+++ b/sheets/민요/검수/사발가.xlsx
@@ -11,7 +11,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <name val="궁서체"/>
@@ -47,6 +47,11 @@
     </font>
     <font>
       <sz val="12"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="18"/>
       <name val="궁서체"/>
       <family val="2"/>
     </font>
@@ -150,7 +155,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -224,6 +229,12 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2928,28 +2939,28 @@
 無</t>
         </is>
       </c>
-      <c r="C3" s="22"/>
+      <c r="C3" s="25"/>
       <c r="D3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 –</t>
         </is>
       </c>
-      <c r="E3" s="22"/>
+      <c r="E3" s="25"/>
       <c r="F3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 潢</t>
         </is>
       </c>
-      <c r="G3" s="22"/>
+      <c r="G3" s="25"/>
       <c r="H3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 潢</t>
         </is>
       </c>
-      <c r="I3" s="24"/>
+      <c r="I3" s="26"/>
     </row>
     <row r="4" ht="108.96" customHeight="1">
       <c r="A4" s="0"/>
@@ -2961,27 +2972,27 @@
 林</t>
         </is>
       </c>
-      <c r="C4" s="22"/>
+      <c r="C4" s="25"/>
       <c r="D4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E4" s="22"/>
+      <c r="E4" s="25"/>
       <c r="F4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 汰</t>
         </is>
       </c>
-      <c r="G4" s="22"/>
+      <c r="G4" s="25"/>
       <c r="H4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 汰</t>
         </is>
       </c>
-      <c r="I4" s="22"/>
+      <c r="I4" s="25"/>
     </row>
     <row r="5" ht="108.96" customHeight="1">
       <c r="A5" s="0"/>
@@ -2992,28 +3003,28 @@
 南</t>
         </is>
       </c>
-      <c r="C5" s="22"/>
+      <c r="C5" s="25"/>
       <c r="D5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 林</t>
         </is>
       </c>
-      <c r="E5" s="22"/>
+      <c r="E5" s="25"/>
       <c r="F5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰</t>
         </is>
       </c>
-      <c r="G5" s="22"/>
+      <c r="G5" s="25"/>
       <c r="H5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 潢</t>
         </is>
       </c>
-      <c r="I5" s="22"/>
+      <c r="I5" s="25"/>
     </row>
     <row r="6" ht="108.96" customHeight="1">
       <c r="A6" s="0"/>
@@ -3024,26 +3035,26 @@
 △</t>
         </is>
       </c>
-      <c r="C6" s="22"/>
+      <c r="C6" s="25"/>
       <c r="D6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 林</t>
         </is>
       </c>
-      <c r="E6" s="22"/>
+      <c r="E6" s="25"/>
       <c r="F6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G6" s="22"/>
+      <c r="G6" s="25"/>
       <c r="H6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I6" s="22"/>
+      <c r="I6" s="25"/>
     </row>
     <row r="7" ht="108.96" customHeight="1">
       <c r="A7" s="0"/>
@@ -3054,28 +3065,28 @@
 –</t>
         </is>
       </c>
-      <c r="C7" s="22"/>
+      <c r="C7" s="25"/>
       <c r="D7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 –</t>
         </is>
       </c>
-      <c r="E7" s="22"/>
+      <c r="E7" s="25"/>
       <c r="F7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">淋
 㴌</t>
         </is>
       </c>
-      <c r="G7" s="22"/>
+      <c r="G7" s="25"/>
       <c r="H7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 㴌</t>
         </is>
       </c>
-      <c r="I7" s="24"/>
+      <c r="I7" s="26"/>
     </row>
     <row r="8" ht="108.96" customHeight="1">
       <c r="A8" s="0"/>
@@ -3085,27 +3096,27 @@
 淋</t>
         </is>
       </c>
-      <c r="C8" s="22"/>
+      <c r="C8" s="25"/>
       <c r="D8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無</t>
         </is>
       </c>
-      <c r="E8" s="22"/>
+      <c r="E8" s="25"/>
       <c r="F8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰</t>
         </is>
       </c>
-      <c r="G8" s="22"/>
+      <c r="G8" s="25"/>
       <c r="H8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰</t>
         </is>
       </c>
-      <c r="I8" s="22"/>
+      <c r="I8" s="25"/>
     </row>
     <row r="9" ht="108.96" customHeight="1">
       <c r="A9" s="0"/>
@@ -3115,28 +3126,28 @@
 –</t>
         </is>
       </c>
-      <c r="C9" s="22"/>
+      <c r="C9" s="25"/>
       <c r="D9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 –</t>
         </is>
       </c>
-      <c r="E9" s="22"/>
+      <c r="E9" s="25"/>
       <c r="F9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 㳞</t>
         </is>
       </c>
-      <c r="G9" s="22"/>
+      <c r="G9" s="25"/>
       <c r="H9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 㳞</t>
         </is>
       </c>
-      <c r="I9" s="24"/>
+      <c r="I9" s="26"/>
     </row>
     <row r="10" ht="108.96" customHeight="1">
       <c r="A10" s="0"/>
@@ -3147,27 +3158,27 @@
 △</t>
         </is>
       </c>
-      <c r="C10" s="22"/>
+      <c r="C10" s="25"/>
       <c r="D10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E10" s="22"/>
+      <c r="E10" s="25"/>
       <c r="F10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰</t>
         </is>
       </c>
-      <c r="G10" s="22"/>
+      <c r="G10" s="25"/>
       <c r="H10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰</t>
         </is>
       </c>
-      <c r="I10" s="22"/>
+      <c r="I10" s="25"/>
     </row>
     <row r="11" ht="108.96" customHeight="1">
       <c r="A11" s="0"/>
@@ -3179,7 +3190,7 @@
 潢</t>
         </is>
       </c>
-      <c r="C11" s="22"/>
+      <c r="C11" s="25"/>
       <c r="D11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
@@ -3187,21 +3198,21 @@
 無</t>
         </is>
       </c>
-      <c r="E11" s="22"/>
+      <c r="E11" s="25"/>
       <c r="F11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 汰</t>
         </is>
       </c>
-      <c r="G11" s="22"/>
+      <c r="G11" s="25"/>
       <c r="H11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
 汰</t>
         </is>
       </c>
-      <c r="I11" s="22"/>
+      <c r="I11" s="25"/>
     </row>
     <row r="12" ht="108.96" customHeight="1">
       <c r="A12" s="0"/>
@@ -3212,25 +3223,25 @@
 –</t>
         </is>
       </c>
-      <c r="C12" s="22"/>
+      <c r="C12" s="25"/>
       <c r="D12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E12" s="22"/>
+      <c r="E12" s="25"/>
       <c r="F12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">黃</t>
         </is>
       </c>
-      <c r="G12" s="22"/>
+      <c r="G12" s="25"/>
       <c r="H12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">黃</t>
         </is>
       </c>
-      <c r="I12" s="22"/>
+      <c r="I12" s="25"/>
     </row>
     <row r="13" ht="108.96" customHeight="1">
       <c r="A13" s="0"/>
@@ -3241,7 +3252,7 @@
 汰</t>
         </is>
       </c>
-      <c r="C13" s="22"/>
+      <c r="C13" s="25"/>
       <c r="D13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
@@ -3250,21 +3261,21 @@
 林</t>
         </is>
       </c>
-      <c r="E13" s="22"/>
+      <c r="E13" s="25"/>
       <c r="F13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 林</t>
         </is>
       </c>
-      <c r="G13" s="22"/>
+      <c r="G13" s="25"/>
       <c r="H13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 林</t>
         </is>
       </c>
-      <c r="I13" s="22"/>
+      <c r="I13" s="25"/>
     </row>
     <row r="14" ht="108.96" customHeight="1">
       <c r="A14" s="0"/>
@@ -3275,7 +3286,7 @@
 △</t>
         </is>
       </c>
-      <c r="C14" s="22"/>
+      <c r="C14" s="25"/>
       <c r="D14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
@@ -3283,21 +3294,21 @@
 林</t>
         </is>
       </c>
-      <c r="E14" s="22"/>
+      <c r="E14" s="25"/>
       <c r="F14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 林</t>
         </is>
       </c>
-      <c r="G14" s="22"/>
+      <c r="G14" s="25"/>
       <c r="H14" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 林</t>
         </is>
       </c>
-      <c r="I14" s="22"/>
+      <c r="I14" s="25"/>
     </row>
     <row r="15" ht="108.96" customHeight="1">
       <c r="A15" s="0"/>
@@ -3308,27 +3319,27 @@
 汰</t>
         </is>
       </c>
-      <c r="C15" s="22"/>
+      <c r="C15" s="25"/>
       <c r="D15" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E15" s="22"/>
+      <c r="E15" s="25"/>
       <c r="F15" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 黃</t>
         </is>
       </c>
-      <c r="G15" s="22"/>
+      <c r="G15" s="25"/>
       <c r="H15" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 黃</t>
         </is>
       </c>
-      <c r="I15" s="22"/>
+      <c r="I15" s="25"/>
     </row>
     <row r="16" ht="108.96" customHeight="1">
       <c r="A16" s="0"/>
@@ -3339,7 +3350,7 @@
 汰</t>
         </is>
       </c>
-      <c r="C16" s="22"/>
+      <c r="C16" s="25"/>
       <c r="D16" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
@@ -3348,21 +3359,21 @@
 南</t>
         </is>
       </c>
-      <c r="E16" s="22"/>
+      <c r="E16" s="25"/>
       <c r="F16" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 林</t>
         </is>
       </c>
-      <c r="G16" s="22"/>
+      <c r="G16" s="25"/>
       <c r="H16" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 林</t>
         </is>
       </c>
-      <c r="I16" s="22"/>
+      <c r="I16" s="25"/>
     </row>
     <row r="17" ht="108.96" customHeight="1">
       <c r="A17" s="0"/>
@@ -3372,27 +3383,27 @@
 –</t>
         </is>
       </c>
-      <c r="C17" s="22"/>
+      <c r="C17" s="25"/>
       <c r="D17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E17" s="22"/>
+      <c r="E17" s="25"/>
       <c r="F17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 –</t>
         </is>
       </c>
-      <c r="G17" s="22"/>
+      <c r="G17" s="25"/>
       <c r="H17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 –</t>
         </is>
       </c>
-      <c r="I17" s="22"/>
+      <c r="I17" s="25"/>
     </row>
     <row r="18" ht="108.96" customHeight="1">
       <c r="A18" s="0"/>
@@ -3403,26 +3414,26 @@
 汰</t>
         </is>
       </c>
-      <c r="C18" s="22"/>
+      <c r="C18" s="25"/>
       <c r="D18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 –</t>
         </is>
       </c>
-      <c r="E18" s="22"/>
+      <c r="E18" s="25"/>
       <c r="F18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林</t>
         </is>
       </c>
-      <c r="G18" s="22"/>
+      <c r="G18" s="25"/>
       <c r="H18" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">林</t>
         </is>
       </c>
-      <c r="I18" s="24"/>
+      <c r="I18" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/sheets/민요/검수/사발가.xlsx
+++ b/sheets/민요/검수/사발가.xlsx
@@ -395,7 +395,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">10-13 전면 재판독. 인쇄 양식(16정간 번호 1~16, 상단 줄 번호 1~8, 하단 "- 196 -")이지만 가로선 없이 번호 2개(1·2, 3·4 …)씩 묶은 큰 칸 8개에 율명이 2~3개씩 쌓여 있음 → 큰 칸 1개 = 정간 1개, 8정간 4/4. 율명은 칸 안 위→아래. 내용은 오른쪽 1~4줄, 5~8줄은 빈 줄이라 #줄수 4. 줄4는 정간 1~4만 있고 5~8은 빈칸. 줄3 정간 5~8은 줄2 정간 1~4와 같은 가락(후렴). 가사는 각 율명 줄 오른쪽 칸(줄1 끝 '데' 아래 쉼표는 생략). 無 오른쪽의 작은 점은 글자 획으로 보고 생략. 칸 끝 6 모양은 △. 한 곡.</t>
+          <t xml:space="preserve">10-13 전면 재판독. 인쇄 양식(16정간 번호 1~16, 상단 줄 번호 1~8, 하단 "- 196 -")이지만 가로선 없이 번호 2개(1·2, 3·4 …)씩 묶은 큰 칸 8개에 율명이 2~3개씩 쌓여 있음 → 큰 칸 1개 = 정간 1개, 8정간 4/4. 율명은 칸 안 위→아래. 내용은 오른쪽 1~4줄, 5~8줄은 빈 줄이라 #줄수 4. 줄4는 정간 1~4만 있고 5~8은 빈칸. 줄3 정간 5~8은 줄2 정간 1~4와 같은 가락(후렴). 가사는 각 율명 줄 오른쪽 칸(줄1 끝 '데' 아래 쉼표는 생략). 無 오른쪽의 작은 점은 글자 획으로 보고 생략. 칸 끝 6 모양은 △. 한 곡. 10-15 潢/㴌 재대조.</t>
         </is>
       </c>
     </row>
@@ -583,13 +583,13 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|潢|–汰</t>
+          <t xml:space="preserve">㴌|㴌|–汰</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
-潢
+          <t xml:space="preserve">㴌
+㴌
 –汰</t>
         </is>
       </c>
@@ -624,13 +624,13 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|潢|–</t>
+          <t xml:space="preserve">㴌|㴌|–</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
-潢
+          <t xml:space="preserve">㴌
+㴌
 –</t>
         </is>
       </c>
@@ -665,14 +665,14 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|潢㳞|潢汰</t>
+          <t xml:space="preserve">㴌|㴌㳞|㴌汰</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
-潢㳞
-潢汰</t>
+          <t xml:space="preserve">㴌
+㴌㳞
+㴌汰</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
@@ -710,14 +710,14 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|–㳞|潢汰</t>
+          <t xml:space="preserve">㴌|–㳞|㴌汰</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
+          <t xml:space="preserve">㴌
 –㳞
-潢汰</t>
+㴌汰</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -915,13 +915,13 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|潢|–汰</t>
+          <t xml:space="preserve">㴌|㴌|–汰</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
-潢
+          <t xml:space="preserve">㴌
+㴌
 –汰</t>
         </is>
       </c>
@@ -956,13 +956,13 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|潢|–</t>
+          <t xml:space="preserve">㴌|㴌|–</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
-潢
+          <t xml:space="preserve">㴌
+㴌
 –</t>
         </is>
       </c>
@@ -997,14 +997,14 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋|潢淋|潢汰</t>
+          <t xml:space="preserve">淋|㴌淋|㴌汰</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">淋
-潢淋
-潢汰</t>
+㴌淋
+㴌汰</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1038,14 +1038,14 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|–淋|潢汰</t>
+          <t xml:space="preserve">㴌|–淋|㴌汰</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
+          <t xml:space="preserve">㴌
 –淋
-潢汰</t>
+㴌汰</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1415,13 +1415,13 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|潢|–汰</t>
+          <t xml:space="preserve">㴌|㴌|–汰</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
-潢
+          <t xml:space="preserve">㴌
+㴌
 –汰</t>
         </is>
       </c>
@@ -1456,13 +1456,13 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|潢|–</t>
+          <t xml:space="preserve">㴌|㴌|–</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
-潢
+          <t xml:space="preserve">㴌
+㴌
 –</t>
         </is>
       </c>
@@ -1497,14 +1497,14 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋|潢淋|潢汰</t>
+          <t xml:space="preserve">淋|㴌淋|㴌汰</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">淋
-潢淋
-潢汰</t>
+㴌淋
+㴌汰</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1538,14 +1538,14 @@
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|–淋|潢汰</t>
+          <t xml:space="preserve">㴌|–淋|㴌汰</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
+          <t xml:space="preserve">㴌
 –淋
-潢汰</t>
+㴌汰</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -1786,8 +1786,8 @@
       </c>
       <c r="F3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
-潢
+          <t xml:space="preserve">㴌
+㴌
 –汰</t>
         </is>
       </c>
@@ -1799,8 +1799,8 @@
       </c>
       <c r="H3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
-潢
+          <t xml:space="preserve">㴌
+㴌
 –汰</t>
         </is>
       </c>
@@ -1842,8 +1842,8 @@
       </c>
       <c r="F4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
-潢
+          <t xml:space="preserve">㴌
+㴌
 –</t>
         </is>
       </c>
@@ -1855,8 +1855,8 @@
       </c>
       <c r="H4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
-潢
+          <t xml:space="preserve">㴌
+㴌
 –</t>
         </is>
       </c>
@@ -1898,8 +1898,8 @@
       <c r="F5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">淋
-潢淋
-潢汰</t>
+㴌淋
+㴌汰</t>
         </is>
       </c>
       <c r="G5" s="25" t="inlineStr">
@@ -1910,9 +1910,9 @@
       </c>
       <c r="H5" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
-潢㳞
-潢汰</t>
+          <t xml:space="preserve">㴌
+㴌㳞
+㴌汰</t>
         </is>
       </c>
       <c r="I5" s="26" t="inlineStr">
@@ -1950,9 +1950,9 @@
       </c>
       <c r="F6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
+          <t xml:space="preserve">㴌
 –淋
-潢汰</t>
+㴌汰</t>
         </is>
       </c>
       <c r="G6" s="27" t="inlineStr">
@@ -1962,9 +1962,9 @@
       </c>
       <c r="H6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
+          <t xml:space="preserve">㴌
 –㳞
-潢汰</t>
+㴌汰</t>
         </is>
       </c>
       <c r="I6" s="27" t="inlineStr">
@@ -1979,8 +1979,8 @@
       <c r="C7" s="22"/>
       <c r="D7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
-潢
+          <t xml:space="preserve">㴌
+㴌
 –汰</t>
         </is>
       </c>
@@ -2026,8 +2026,8 @@
       <c r="C8" s="25"/>
       <c r="D8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
-潢
+          <t xml:space="preserve">㴌
+㴌
 –</t>
         </is>
       </c>
@@ -2071,8 +2071,8 @@
       <c r="D9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">淋
-潢淋
-潢汰</t>
+㴌淋
+㴌汰</t>
         </is>
       </c>
       <c r="E9" s="25" t="inlineStr">
@@ -2114,9 +2114,9 @@
       <c r="C10" s="27"/>
       <c r="D10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
+          <t xml:space="preserve">㴌
 –淋
-潢汰</t>
+㴌汰</t>
         </is>
       </c>
       <c r="E10" s="27" t="inlineStr">

--- a/sheets/민요/검수/사발가.xlsx
+++ b/sheets/민요/검수/사발가.xlsx
@@ -65,10 +65,7 @@
       </patternFill>
     </fill>
     <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="solid">

--- a/sheets/민요/검수/사발가.xlsx
+++ b/sheets/민요/검수/사발가.xlsx
@@ -1724,6 +1724,9 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
@@ -1736,10 +1739,10 @@
     <col min="9" max="9" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="77.61" customHeight="1">
+    <row r="2" ht="40.82" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -1754,7 +1757,7 @@
       <c r="H2" s="20"/>
       <c r="I2" s="20"/>
     </row>
-    <row r="3" ht="77.61" customHeight="1">
+    <row r="3" ht="90.88" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -1808,7 +1811,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="77.61" customHeight="1">
+    <row r="4" ht="90.88" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -1864,7 +1867,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="77.61" customHeight="1">
+    <row r="5" ht="90.88" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -1919,7 +1922,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="77.61" customHeight="1">
+    <row r="6" ht="90.88" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -1970,7 +1973,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="77.61" customHeight="1">
+    <row r="7" ht="90.88" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21"/>
       <c r="C7" s="22"/>
@@ -2017,7 +2020,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="77.61" customHeight="1">
+    <row r="8" ht="90.88" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21"/>
       <c r="C8" s="25"/>
@@ -2061,7 +2064,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="77.61" customHeight="1">
+    <row r="9" ht="90.88" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21"/>
       <c r="C9" s="25"/>
@@ -2105,7 +2108,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="77.61" customHeight="1">
+    <row r="10" ht="90.88" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21"/>
       <c r="C10" s="27"/>
@@ -2152,6 +2155,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="100"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="98"/>
 </worksheet>
 </file>
--- a/sheets/민요/검수/사발가.xlsx
+++ b/sheets/민요/검수/사발가.xlsx
@@ -1729,13 +1729,13 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="12" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
   </cols>
   <sheetData>
